--- a/기준_와.xlsx
+++ b/기준_와.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dltkd\OneDrive\바탕 화면\발주서 자동화\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003B19A6-71E9-47BF-9AE9-282FBF58C09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="7970" yWindow="1650" windowWidth="27640" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -7015,12 +7021,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -7028,8 +7034,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -7075,17 +7088,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7123,7 +7144,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -7157,6 +7178,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -7191,9 +7213,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7366,11 +7389,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D777"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="36.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7384,7 +7412,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -7398,7 +7426,7 @@
         <v>10600</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -7412,7 +7440,7 @@
         <v>10600</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -7426,7 +7454,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -7440,7 +7468,7 @@
         <v>5570</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -7454,7 +7482,7 @@
         <v>6258</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7468,7 +7496,7 @@
         <v>5662</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -7482,7 +7510,7 @@
         <v>6270</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -7496,7 +7524,7 @@
         <v>7040</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -7510,7 +7538,7 @@
         <v>4160</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7524,7 +7552,7 @@
         <v>4160</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -7538,7 +7566,7 @@
         <v>6885</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -7552,7 +7580,7 @@
         <v>7491</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -7566,7 +7594,7 @@
         <v>13480</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -7580,7 +7608,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -7594,7 +7622,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -7608,7 +7636,7 @@
         <v>9350</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -7622,7 +7650,7 @@
         <v>13480</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -7636,7 +7664,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -7650,7 +7678,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -7664,7 +7692,7 @@
         <v>11200</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -7678,7 +7706,7 @@
         <v>11200</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -7692,7 +7720,7 @@
         <v>9700</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -7706,7 +7734,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -7720,7 +7748,7 @@
         <v>7170</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -7734,7 +7762,7 @@
         <v>7940</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -7748,7 +7776,7 @@
         <v>7940</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -7762,7 +7790,7 @@
         <v>4280</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -7776,7 +7804,7 @@
         <v>4280</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -7790,7 +7818,7 @@
         <v>5886</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -7804,7 +7832,7 @@
         <v>5991</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -7818,7 +7846,7 @@
         <v>6662</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -7832,7 +7860,7 @@
         <v>5618</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -7846,7 +7874,7 @@
         <v>5480</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -7860,7 +7888,7 @@
         <v>8700</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -7874,7 +7902,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -7888,7 +7916,7 @@
         <v>6910</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -7902,7 +7930,7 @@
         <v>6750</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -7916,7 +7944,7 @@
         <v>3315</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -7930,7 +7958,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -7944,7 +7972,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -7958,7 +7986,7 @@
         <v>6660</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -7972,7 +8000,7 @@
         <v>6660</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -7986,7 +8014,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -8000,7 +8028,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -8014,7 +8042,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -8028,7 +8056,7 @@
         <v>4680</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -8042,7 +8070,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -8056,7 +8084,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -8070,7 +8098,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -8084,7 +8112,7 @@
         <v>4767</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -8098,7 +8126,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -8112,7 +8140,7 @@
         <v>5240</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -8126,7 +8154,7 @@
         <v>4612</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -8140,7 +8168,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -8154,7 +8182,7 @@
         <v>3283</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -8168,7 +8196,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -8182,7 +8210,7 @@
         <v>5240</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -8196,7 +8224,7 @@
         <v>6860</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -8210,7 +8238,7 @@
         <v>5088</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -8224,7 +8252,7 @@
         <v>7040</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -8238,7 +8266,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -8252,7 +8280,7 @@
         <v>7040</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -8266,7 +8294,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -8280,7 +8308,7 @@
         <v>7040</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -8294,7 +8322,7 @@
         <v>7169</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -8308,7 +8336,7 @@
         <v>7169</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -8322,7 +8350,7 @@
         <v>7890</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -8336,7 +8364,7 @@
         <v>7890</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -8350,7 +8378,7 @@
         <v>9610</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -8364,7 +8392,7 @@
         <v>9610</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -8378,7 +8406,7 @@
         <v>5246</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -8392,7 +8420,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -8406,7 +8434,7 @@
         <v>4765</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -8420,7 +8448,7 @@
         <v>4991</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -8434,7 +8462,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -8448,7 +8476,7 @@
         <v>5552</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -8462,7 +8490,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -8476,7 +8504,7 @@
         <v>5164</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -8490,7 +8518,7 @@
         <v>15350</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -8504,7 +8532,7 @@
         <v>6134</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -8518,7 +8546,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -8532,7 +8560,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -8546,7 +8574,7 @@
         <v>7890</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -8560,7 +8588,7 @@
         <v>5077</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -8574,7 +8602,7 @@
         <v>7040</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -8588,7 +8616,7 @@
         <v>7040</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -8602,7 +8630,7 @@
         <v>7040</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -8616,7 +8644,7 @@
         <v>5149</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -8630,7 +8658,7 @@
         <v>5015</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -8644,7 +8672,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -8658,7 +8686,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -8672,7 +8700,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -8686,7 +8714,7 @@
         <v>5266</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -8700,7 +8728,7 @@
         <v>5361</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -8714,7 +8742,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -8728,7 +8756,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -8742,7 +8770,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>101</v>
       </c>
@@ -8756,7 +8784,7 @@
         <v>8945</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -8770,7 +8798,7 @@
         <v>8974</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>103</v>
       </c>
@@ -8784,7 +8812,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -8798,7 +8826,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -8812,7 +8840,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>106</v>
       </c>
@@ -8826,7 +8854,7 @@
         <v>5878</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -8840,7 +8868,7 @@
         <v>14156</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -8854,7 +8882,7 @@
         <v>13360</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>109</v>
       </c>
@@ -8868,7 +8896,7 @@
         <v>7169</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -8882,7 +8910,7 @@
         <v>6032</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -8896,7 +8924,7 @@
         <v>6440</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>112</v>
       </c>
@@ -8910,7 +8938,7 @@
         <v>6236</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>113</v>
       </c>
@@ -8924,7 +8952,7 @@
         <v>5829</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -8938,7 +8966,7 @@
         <v>7169</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -8952,7 +8980,7 @@
         <v>7169</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -8966,7 +8994,7 @@
         <v>7169</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -8980,7 +9008,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -8994,7 +9022,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -9008,7 +9036,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -9022,7 +9050,7 @@
         <v>5869</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -9036,7 +9064,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>122</v>
       </c>
@@ -9050,7 +9078,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>123</v>
       </c>
@@ -9064,7 +9092,7 @@
         <v>7685</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>124</v>
       </c>
@@ -9078,7 +9106,7 @@
         <v>7622</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>125</v>
       </c>
@@ -9092,7 +9120,7 @@
         <v>7800</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>126</v>
       </c>
@@ -9106,7 +9134,7 @@
         <v>5134</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -9120,7 +9148,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>128</v>
       </c>
@@ -9134,7 +9162,7 @@
         <v>5698</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>129</v>
       </c>
@@ -9148,7 +9176,7 @@
         <v>6400</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>130</v>
       </c>
@@ -9162,7 +9190,7 @@
         <v>6400</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>131</v>
       </c>
@@ -9176,7 +9204,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>132</v>
       </c>
@@ -9190,7 +9218,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>133</v>
       </c>
@@ -9204,7 +9232,7 @@
         <v>6910</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>134</v>
       </c>
@@ -9218,7 +9246,7 @@
         <v>4979</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>135</v>
       </c>
@@ -9232,7 +9260,7 @@
         <v>4845</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>136</v>
       </c>
@@ -9246,7 +9274,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>137</v>
       </c>
@@ -9260,7 +9288,7 @@
         <v>14744</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>138</v>
       </c>
@@ -9274,7 +9302,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -9288,7 +9316,7 @@
         <v>5876</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -9302,7 +9330,7 @@
         <v>6321</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>141</v>
       </c>
@@ -9316,7 +9344,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -9330,7 +9358,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>143</v>
       </c>
@@ -9344,7 +9372,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>144</v>
       </c>
@@ -9358,7 +9386,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>145</v>
       </c>
@@ -9372,7 +9400,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -9386,7 +9414,7 @@
         <v>6253</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -9400,7 +9428,7 @@
         <v>6348</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>148</v>
       </c>
@@ -9414,7 +9442,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>149</v>
       </c>
@@ -9428,7 +9456,7 @@
         <v>6949</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -9442,7 +9470,7 @@
         <v>7204</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>151</v>
       </c>
@@ -9456,7 +9484,7 @@
         <v>6373</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>152</v>
       </c>
@@ -9470,7 +9498,7 @@
         <v>6545</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>153</v>
       </c>
@@ -9484,7 +9512,7 @@
         <v>6308</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -9498,7 +9526,7 @@
         <v>7085</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>155</v>
       </c>
@@ -9512,7 +9540,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>156</v>
       </c>
@@ -9526,7 +9554,7 @@
         <v>8734</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>157</v>
       </c>
@@ -9540,7 +9568,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>158</v>
       </c>
@@ -9554,7 +9582,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>159</v>
       </c>
@@ -9568,7 +9596,7 @@
         <v>18100</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -9582,7 +9610,7 @@
         <v>18100</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>161</v>
       </c>
@@ -9596,7 +9624,7 @@
         <v>18100</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -9610,7 +9638,7 @@
         <v>18100</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>163</v>
       </c>
@@ -9624,7 +9652,7 @@
         <v>18100</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>164</v>
       </c>
@@ -9638,7 +9666,7 @@
         <v>6305</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>165</v>
       </c>
@@ -9652,7 +9680,7 @@
         <v>6432</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -9666,7 +9694,7 @@
         <v>6860</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>167</v>
       </c>
@@ -9680,7 +9708,7 @@
         <v>6668</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>168</v>
       </c>
@@ -9694,7 +9722,7 @@
         <v>7085</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>169</v>
       </c>
@@ -9708,7 +9736,7 @@
         <v>25909</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>170</v>
       </c>
@@ -9722,7 +9750,7 @@
         <v>28500</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>171</v>
       </c>
@@ -9736,7 +9764,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>172</v>
       </c>
@@ -9750,7 +9778,7 @@
         <v>4255</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>173</v>
       </c>
@@ -9764,7 +9792,7 @@
         <v>4072</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>174</v>
       </c>
@@ -9778,7 +9806,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>175</v>
       </c>
@@ -9792,7 +9820,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>176</v>
       </c>
@@ -9806,7 +9834,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>177</v>
       </c>
@@ -9820,7 +9848,7 @@
         <v>5930</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>178</v>
       </c>
@@ -9834,7 +9862,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>179</v>
       </c>
@@ -9848,7 +9876,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>180</v>
       </c>
@@ -9862,7 +9890,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>181</v>
       </c>
@@ -9876,7 +9904,7 @@
         <v>4262</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>182</v>
       </c>
@@ -9890,7 +9918,7 @@
         <v>5304</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>183</v>
       </c>
@@ -9904,7 +9932,7 @@
         <v>5527</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>184</v>
       </c>
@@ -9918,7 +9946,7 @@
         <v>5664</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>185</v>
       </c>
@@ -9932,7 +9960,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>186</v>
       </c>
@@ -9946,7 +9974,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>187</v>
       </c>
@@ -9960,7 +9988,7 @@
         <v>4370</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -9974,7 +10002,7 @@
         <v>4370</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>189</v>
       </c>
@@ -9988,7 +10016,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>190</v>
       </c>
@@ -10002,7 +10030,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>191</v>
       </c>
@@ -10016,7 +10044,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>192</v>
       </c>
@@ -10030,7 +10058,7 @@
         <v>5708</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>193</v>
       </c>
@@ -10044,7 +10072,7 @@
         <v>4370</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>194</v>
       </c>
@@ -10058,7 +10086,7 @@
         <v>8613</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>195</v>
       </c>
@@ -10072,7 +10100,7 @@
         <v>7660</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>196</v>
       </c>
@@ -10086,7 +10114,7 @@
         <v>15770</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>197</v>
       </c>
@@ -10100,7 +10128,7 @@
         <v>7971</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -10114,7 +10142,7 @@
         <v>11417</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -10128,7 +10156,7 @@
         <v>4133</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>200</v>
       </c>
@@ -10142,7 +10170,7 @@
         <v>5815</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>201</v>
       </c>
@@ -10156,7 +10184,7 @@
         <v>5260</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>202</v>
       </c>
@@ -10170,7 +10198,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>203</v>
       </c>
@@ -10184,7 +10212,7 @@
         <v>5260</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>204</v>
       </c>
@@ -10198,7 +10226,7 @@
         <v>10333</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>205</v>
       </c>
@@ -10212,7 +10240,7 @@
         <v>12127</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>206</v>
       </c>
@@ -10226,7 +10254,7 @@
         <v>7044</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>207</v>
       </c>
@@ -10240,7 +10268,7 @@
         <v>6714</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>208</v>
       </c>
@@ -10254,7 +10282,7 @@
         <v>5107</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>209</v>
       </c>
@@ -10268,7 +10296,7 @@
         <v>5148</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>210</v>
       </c>
@@ -10282,7 +10310,7 @@
         <v>8920</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>211</v>
       </c>
@@ -10296,7 +10324,7 @@
         <v>8920</v>
       </c>
     </row>
-    <row r="210" spans="1:4">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>212</v>
       </c>
@@ -10310,7 +10338,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>213</v>
       </c>
@@ -10324,7 +10352,7 @@
         <v>8480</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>214</v>
       </c>
@@ -10338,7 +10366,7 @@
         <v>13786</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>215</v>
       </c>
@@ -10352,7 +10380,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>216</v>
       </c>
@@ -10366,7 +10394,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>217</v>
       </c>
@@ -10380,7 +10408,7 @@
         <v>7257</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>218</v>
       </c>
@@ -10394,7 +10422,7 @@
         <v>7257</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>219</v>
       </c>
@@ -10408,7 +10436,7 @@
         <v>11821</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>220</v>
       </c>
@@ -10422,7 +10450,7 @@
         <v>12983</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>221</v>
       </c>
@@ -10436,7 +10464,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>222</v>
       </c>
@@ -10450,7 +10478,7 @@
         <v>10400</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>223</v>
       </c>
@@ -10464,7 +10492,7 @@
         <v>8486</v>
       </c>
     </row>
-    <row r="222" spans="1:4">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>224</v>
       </c>
@@ -10478,7 +10506,7 @@
         <v>8725</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>225</v>
       </c>
@@ -10492,7 +10520,7 @@
         <v>10155</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>226</v>
       </c>
@@ -10506,7 +10534,7 @@
         <v>11933</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>227</v>
       </c>
@@ -10520,7 +10548,7 @@
         <v>6817</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>228</v>
       </c>
@@ -10534,7 +10562,7 @@
         <v>6492</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>229</v>
       </c>
@@ -10548,7 +10576,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>230</v>
       </c>
@@ -10562,7 +10590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>231</v>
       </c>
@@ -10576,7 +10604,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>232</v>
       </c>
@@ -10590,7 +10618,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>233</v>
       </c>
@@ -10604,7 +10632,7 @@
         <v>10318</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>234</v>
       </c>
@@ -10618,7 +10646,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>235</v>
       </c>
@@ -10632,7 +10660,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>236</v>
       </c>
@@ -10646,7 +10674,7 @@
         <v>6110</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>237</v>
       </c>
@@ -10660,7 +10688,7 @@
         <v>6140</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>238</v>
       </c>
@@ -10674,7 +10702,7 @@
         <v>7800</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>239</v>
       </c>
@@ -10688,7 +10716,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>240</v>
       </c>
@@ -10702,7 +10730,7 @@
         <v>11320</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>241</v>
       </c>
@@ -10716,7 +10744,7 @@
         <v>11320</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>242</v>
       </c>
@@ -10730,7 +10758,7 @@
         <v>11320</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>243</v>
       </c>
@@ -10744,7 +10772,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>244</v>
       </c>
@@ -10758,7 +10786,7 @@
         <v>11128</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>245</v>
       </c>
@@ -10772,7 +10800,7 @@
         <v>11192</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>246</v>
       </c>
@@ -10786,7 +10814,7 @@
         <v>11112</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>247</v>
       </c>
@@ -10800,7 +10828,7 @@
         <v>11320</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>248</v>
       </c>
@@ -10814,7 +10842,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>249</v>
       </c>
@@ -10828,7 +10856,7 @@
         <v>9710</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>250</v>
       </c>
@@ -10842,7 +10870,7 @@
         <v>9710</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>251</v>
       </c>
@@ -10856,7 +10884,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>252</v>
       </c>
@@ -10870,7 +10898,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>253</v>
       </c>
@@ -10884,7 +10912,7 @@
         <v>12760</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>254</v>
       </c>
@@ -10898,7 +10926,7 @@
         <v>12760</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>255</v>
       </c>
@@ -10912,7 +10940,7 @@
         <v>12760</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>256</v>
       </c>
@@ -10926,7 +10954,7 @@
         <v>12760</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>257</v>
       </c>
@@ -10940,7 +10968,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>258</v>
       </c>
@@ -10954,7 +10982,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>259</v>
       </c>
@@ -10968,7 +10996,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>260</v>
       </c>
@@ -10982,7 +11010,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>261</v>
       </c>
@@ -10996,7 +11024,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>262</v>
       </c>
@@ -11010,7 +11038,7 @@
         <v>23116</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>263</v>
       </c>
@@ -11024,7 +11052,7 @@
         <v>5700</v>
       </c>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>264</v>
       </c>
@@ -11038,7 +11066,7 @@
         <v>5700</v>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>265</v>
       </c>
@@ -11052,7 +11080,7 @@
         <v>8231</v>
       </c>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>266</v>
       </c>
@@ -11066,7 +11094,7 @@
         <v>7440</v>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>267</v>
       </c>
@@ -11080,7 +11108,7 @@
         <v>7440</v>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>268</v>
       </c>
@@ -11094,7 +11122,7 @@
         <v>7440</v>
       </c>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>269</v>
       </c>
@@ -11108,7 +11136,7 @@
         <v>7440</v>
       </c>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>270</v>
       </c>
@@ -11122,7 +11150,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>271</v>
       </c>
@@ -11136,7 +11164,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>272</v>
       </c>
@@ -11150,7 +11178,7 @@
         <v>9755</v>
       </c>
     </row>
-    <row r="271" spans="1:4">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>273</v>
       </c>
@@ -11164,7 +11192,7 @@
         <v>9723</v>
       </c>
     </row>
-    <row r="272" spans="1:4">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>274</v>
       </c>
@@ -11178,7 +11206,7 @@
         <v>9713</v>
       </c>
     </row>
-    <row r="273" spans="1:4">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>275</v>
       </c>
@@ -11192,7 +11220,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="274" spans="1:4">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>276</v>
       </c>
@@ -11206,7 +11234,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>277</v>
       </c>
@@ -11220,7 +11248,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="276" spans="1:4">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>278</v>
       </c>
@@ -11234,7 +11262,7 @@
         <v>3582</v>
       </c>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>279</v>
       </c>
@@ -11248,7 +11276,7 @@
         <v>12947</v>
       </c>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>280</v>
       </c>
@@ -11262,7 +11290,7 @@
         <v>6550</v>
       </c>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>281</v>
       </c>
@@ -11276,7 +11304,7 @@
         <v>3439</v>
       </c>
     </row>
-    <row r="280" spans="1:4">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>282</v>
       </c>
@@ -11290,7 +11318,7 @@
         <v>6550</v>
       </c>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>283</v>
       </c>
@@ -11304,7 +11332,7 @@
         <v>6550</v>
       </c>
     </row>
-    <row r="282" spans="1:4">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>284</v>
       </c>
@@ -11318,7 +11346,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>285</v>
       </c>
@@ -11332,7 +11360,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>286</v>
       </c>
@@ -11346,7 +11374,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>287</v>
       </c>
@@ -11360,7 +11388,7 @@
         <v>10740</v>
       </c>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>288</v>
       </c>
@@ -11374,7 +11402,7 @@
         <v>5466</v>
       </c>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>289</v>
       </c>
@@ -11388,7 +11416,7 @@
         <v>5098</v>
       </c>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>290</v>
       </c>
@@ -11402,7 +11430,7 @@
         <v>5700</v>
       </c>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>291</v>
       </c>
@@ -11416,7 +11444,7 @@
         <v>5018</v>
       </c>
     </row>
-    <row r="290" spans="1:4">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>292</v>
       </c>
@@ -11430,7 +11458,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>293</v>
       </c>
@@ -11444,7 +11472,7 @@
         <v>3270</v>
       </c>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>294</v>
       </c>
@@ -11458,7 +11486,7 @@
         <v>12600</v>
       </c>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>295</v>
       </c>
@@ -11472,7 +11500,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="294" spans="1:4">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>296</v>
       </c>
@@ -11486,7 +11514,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="295" spans="1:4">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>297</v>
       </c>
@@ -11500,7 +11528,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="296" spans="1:4">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>298</v>
       </c>
@@ -11514,7 +11542,7 @@
         <v>6779</v>
       </c>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>299</v>
       </c>
@@ -11528,7 +11556,7 @@
         <v>6103</v>
       </c>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>300</v>
       </c>
@@ -11542,7 +11570,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>301</v>
       </c>
@@ -11556,7 +11584,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>302</v>
       </c>
@@ -11570,7 +11598,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>303</v>
       </c>
@@ -11584,7 +11612,7 @@
         <v>4960</v>
       </c>
     </row>
-    <row r="302" spans="1:4">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>304</v>
       </c>
@@ -11598,7 +11626,7 @@
         <v>4960</v>
       </c>
     </row>
-    <row r="303" spans="1:4">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>305</v>
       </c>
@@ -11612,7 +11640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:4">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>306</v>
       </c>
@@ -11626,7 +11654,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>307</v>
       </c>
@@ -11640,7 +11668,7 @@
         <v>6634</v>
       </c>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>308</v>
       </c>
@@ -11654,7 +11682,7 @@
         <v>4142</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>309</v>
       </c>
@@ -11668,7 +11696,7 @@
         <v>3783</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>310</v>
       </c>
@@ -11682,7 +11710,7 @@
         <v>15800</v>
       </c>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>311</v>
       </c>
@@ -11696,7 +11724,7 @@
         <v>5958</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>312</v>
       </c>
@@ -11710,7 +11738,7 @@
         <v>23138</v>
       </c>
     </row>
-    <row r="311" spans="1:4">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>313</v>
       </c>
@@ -11724,7 +11752,7 @@
         <v>23138</v>
       </c>
     </row>
-    <row r="312" spans="1:4">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>314</v>
       </c>
@@ -11738,7 +11766,7 @@
         <v>5689</v>
       </c>
     </row>
-    <row r="313" spans="1:4">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>315</v>
       </c>
@@ -11752,7 +11780,7 @@
         <v>3442</v>
       </c>
     </row>
-    <row r="314" spans="1:4">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>316</v>
       </c>
@@ -11766,7 +11794,7 @@
         <v>3515</v>
       </c>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>317</v>
       </c>
@@ -11780,7 +11808,7 @@
         <v>3466</v>
       </c>
     </row>
-    <row r="316" spans="1:4">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>318</v>
       </c>
@@ -11794,7 +11822,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="317" spans="1:4">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>319</v>
       </c>
@@ -11808,7 +11836,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>320</v>
       </c>
@@ -11822,7 +11850,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>321</v>
       </c>
@@ -11836,7 +11864,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>322</v>
       </c>
@@ -11850,7 +11878,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>323</v>
       </c>
@@ -11864,7 +11892,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>324</v>
       </c>
@@ -11878,7 +11906,7 @@
         <v>5968</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>325</v>
       </c>
@@ -11892,7 +11920,7 @@
         <v>6474</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>326</v>
       </c>
@@ -11906,7 +11934,7 @@
         <v>6474</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>327</v>
       </c>
@@ -11920,7 +11948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>328</v>
       </c>
@@ -11934,7 +11962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>329</v>
       </c>
@@ -11948,7 +11976,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="328" spans="1:4">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>330</v>
       </c>
@@ -11962,7 +11990,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>331</v>
       </c>
@@ -11976,7 +12004,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>332</v>
       </c>
@@ -11990,7 +12018,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>333</v>
       </c>
@@ -12004,7 +12032,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>334</v>
       </c>
@@ -12018,7 +12046,7 @@
         <v>4890</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>335</v>
       </c>
@@ -12032,7 +12060,7 @@
         <v>2785</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>336</v>
       </c>
@@ -12046,7 +12074,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>337</v>
       </c>
@@ -12060,7 +12088,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>338</v>
       </c>
@@ -12074,7 +12102,7 @@
         <v>3327</v>
       </c>
     </row>
-    <row r="337" spans="1:4">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>339</v>
       </c>
@@ -12088,7 +12116,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="338" spans="1:4">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>340</v>
       </c>
@@ -12102,7 +12130,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>341</v>
       </c>
@@ -12116,7 +12144,7 @@
         <v>3894</v>
       </c>
     </row>
-    <row r="340" spans="1:4">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>342</v>
       </c>
@@ -12130,7 +12158,7 @@
         <v>3864</v>
       </c>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>343</v>
       </c>
@@ -12144,7 +12172,7 @@
         <v>3886</v>
       </c>
     </row>
-    <row r="342" spans="1:4">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>344</v>
       </c>
@@ -12158,7 +12186,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="343" spans="1:4">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>345</v>
       </c>
@@ -12172,7 +12200,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="344" spans="1:4">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>346</v>
       </c>
@@ -12186,7 +12214,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="345" spans="1:4">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>347</v>
       </c>
@@ -12200,7 +12228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:4">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>348</v>
       </c>
@@ -12214,7 +12242,7 @@
         <v>3666</v>
       </c>
     </row>
-    <row r="347" spans="1:4">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>349</v>
       </c>
@@ -12228,7 +12256,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="348" spans="1:4">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>350</v>
       </c>
@@ -12242,7 +12270,7 @@
         <v>4745</v>
       </c>
     </row>
-    <row r="349" spans="1:4">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>351</v>
       </c>
@@ -12256,7 +12284,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="350" spans="1:4">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>352</v>
       </c>
@@ -12270,7 +12298,7 @@
         <v>7470</v>
       </c>
     </row>
-    <row r="351" spans="1:4">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>353</v>
       </c>
@@ -12284,7 +12312,7 @@
         <v>7470</v>
       </c>
     </row>
-    <row r="352" spans="1:4">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>354</v>
       </c>
@@ -12298,7 +12326,7 @@
         <v>7470</v>
       </c>
     </row>
-    <row r="353" spans="1:4">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>355</v>
       </c>
@@ -12312,7 +12340,7 @@
         <v>4860</v>
       </c>
     </row>
-    <row r="354" spans="1:4">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>356</v>
       </c>
@@ -12326,7 +12354,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="355" spans="1:4">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>357</v>
       </c>
@@ -12340,7 +12368,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="356" spans="1:4">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>358</v>
       </c>
@@ -12354,7 +12382,7 @@
         <v>7470</v>
       </c>
     </row>
-    <row r="357" spans="1:4">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>359</v>
       </c>
@@ -12368,7 +12396,7 @@
         <v>7113</v>
       </c>
     </row>
-    <row r="358" spans="1:4">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>360</v>
       </c>
@@ -12382,7 +12410,7 @@
         <v>6578</v>
       </c>
     </row>
-    <row r="359" spans="1:4">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>361</v>
       </c>
@@ -12396,7 +12424,7 @@
         <v>6614</v>
       </c>
     </row>
-    <row r="360" spans="1:4">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>362</v>
       </c>
@@ -12410,7 +12438,7 @@
         <v>3767</v>
       </c>
     </row>
-    <row r="361" spans="1:4">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>363</v>
       </c>
@@ -12424,7 +12452,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="362" spans="1:4">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>364</v>
       </c>
@@ -12438,7 +12466,7 @@
         <v>3822</v>
       </c>
     </row>
-    <row r="363" spans="1:4">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>365</v>
       </c>
@@ -12452,7 +12480,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="364" spans="1:4">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>366</v>
       </c>
@@ -12466,7 +12494,7 @@
         <v>5196</v>
       </c>
     </row>
-    <row r="365" spans="1:4">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>367</v>
       </c>
@@ -12480,7 +12508,7 @@
         <v>5447</v>
       </c>
     </row>
-    <row r="366" spans="1:4">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>368</v>
       </c>
@@ -12494,7 +12522,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="367" spans="1:4">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>369</v>
       </c>
@@ -12508,7 +12536,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="368" spans="1:4">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>370</v>
       </c>
@@ -12522,7 +12550,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="369" spans="1:4">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>371</v>
       </c>
@@ -12536,7 +12564,7 @@
         <v>3633</v>
       </c>
     </row>
-    <row r="370" spans="1:4">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>372</v>
       </c>
@@ -12550,7 +12578,7 @@
         <v>3633</v>
       </c>
     </row>
-    <row r="371" spans="1:4">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>373</v>
       </c>
@@ -12564,7 +12592,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="372" spans="1:4">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>374</v>
       </c>
@@ -12578,7 +12606,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="373" spans="1:4">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>375</v>
       </c>
@@ -12592,7 +12620,7 @@
         <v>3180</v>
       </c>
     </row>
-    <row r="374" spans="1:4">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>376</v>
       </c>
@@ -12606,7 +12634,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="375" spans="1:4">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>377</v>
       </c>
@@ -12620,7 +12648,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="376" spans="1:4">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>378</v>
       </c>
@@ -12634,7 +12662,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="377" spans="1:4">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>379</v>
       </c>
@@ -12648,7 +12676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:4">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>380</v>
       </c>
@@ -12662,7 +12690,7 @@
         <v>4888</v>
       </c>
     </row>
-    <row r="379" spans="1:4">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>381</v>
       </c>
@@ -12676,7 +12704,7 @@
         <v>4942</v>
       </c>
     </row>
-    <row r="380" spans="1:4">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>382</v>
       </c>
@@ -12690,7 +12718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:4">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>383</v>
       </c>
@@ -12704,7 +12732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:4">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>384</v>
       </c>
@@ -12718,7 +12746,7 @@
         <v>7030</v>
       </c>
     </row>
-    <row r="383" spans="1:4">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>385</v>
       </c>
@@ -12732,7 +12760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:4">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>386</v>
       </c>
@@ -12746,7 +12774,7 @@
         <v>4951</v>
       </c>
     </row>
-    <row r="385" spans="1:4">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>387</v>
       </c>
@@ -12760,7 +12788,7 @@
         <v>5754</v>
       </c>
     </row>
-    <row r="386" spans="1:4">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>388</v>
       </c>
@@ -12774,7 +12802,7 @@
         <v>5503</v>
       </c>
     </row>
-    <row r="387" spans="1:4">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>389</v>
       </c>
@@ -12788,7 +12816,7 @@
         <v>5717</v>
       </c>
     </row>
-    <row r="388" spans="1:4">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>390</v>
       </c>
@@ -12802,7 +12830,7 @@
         <v>6360</v>
       </c>
     </row>
-    <row r="389" spans="1:4">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>391</v>
       </c>
@@ -12816,7 +12844,7 @@
         <v>6360</v>
       </c>
     </row>
-    <row r="390" spans="1:4">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>392</v>
       </c>
@@ -12830,7 +12858,7 @@
         <v>4925</v>
       </c>
     </row>
-    <row r="391" spans="1:4">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>393</v>
       </c>
@@ -12844,7 +12872,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="392" spans="1:4">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>394</v>
       </c>
@@ -12858,7 +12886,7 @@
         <v>3830</v>
       </c>
     </row>
-    <row r="393" spans="1:4">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>395</v>
       </c>
@@ -12872,7 +12900,7 @@
         <v>3508</v>
       </c>
     </row>
-    <row r="394" spans="1:4">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>396</v>
       </c>
@@ -12886,7 +12914,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="395" spans="1:4">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>397</v>
       </c>
@@ -12900,7 +12928,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="396" spans="1:4">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>398</v>
       </c>
@@ -12914,7 +12942,7 @@
         <v>4247</v>
       </c>
     </row>
-    <row r="397" spans="1:4">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>399</v>
       </c>
@@ -12928,7 +12956,7 @@
         <v>4189</v>
       </c>
     </row>
-    <row r="398" spans="1:4">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>400</v>
       </c>
@@ -12942,7 +12970,7 @@
         <v>4398</v>
       </c>
     </row>
-    <row r="399" spans="1:4">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>401</v>
       </c>
@@ -12956,7 +12984,7 @@
         <v>7520</v>
       </c>
     </row>
-    <row r="400" spans="1:4">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>402</v>
       </c>
@@ -12970,7 +12998,7 @@
         <v>6825</v>
       </c>
     </row>
-    <row r="401" spans="1:4">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>403</v>
       </c>
@@ -12984,7 +13012,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="402" spans="1:4">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>404</v>
       </c>
@@ -12998,7 +13026,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="403" spans="1:4">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>405</v>
       </c>
@@ -13012,7 +13040,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="404" spans="1:4">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>406</v>
       </c>
@@ -13026,7 +13054,7 @@
         <v>4628</v>
       </c>
     </row>
-    <row r="405" spans="1:4">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>407</v>
       </c>
@@ -13040,7 +13068,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="406" spans="1:4">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>408</v>
       </c>
@@ -13054,7 +13082,7 @@
         <v>4924</v>
       </c>
     </row>
-    <row r="407" spans="1:4">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>409</v>
       </c>
@@ -13068,7 +13096,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="408" spans="1:4">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>410</v>
       </c>
@@ -13082,7 +13110,7 @@
         <v>5145</v>
       </c>
     </row>
-    <row r="409" spans="1:4">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>411</v>
       </c>
@@ -13096,7 +13124,7 @@
         <v>4884</v>
       </c>
     </row>
-    <row r="410" spans="1:4">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>412</v>
       </c>
@@ -13110,7 +13138,7 @@
         <v>4890</v>
       </c>
     </row>
-    <row r="411" spans="1:4">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>413</v>
       </c>
@@ -13124,7 +13152,7 @@
         <v>4822</v>
       </c>
     </row>
-    <row r="412" spans="1:4">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>414</v>
       </c>
@@ -13138,7 +13166,7 @@
         <v>4446</v>
       </c>
     </row>
-    <row r="413" spans="1:4">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>415</v>
       </c>
@@ -13152,7 +13180,7 @@
         <v>4454</v>
       </c>
     </row>
-    <row r="414" spans="1:4">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>416</v>
       </c>
@@ -13166,7 +13194,7 @@
         <v>4609</v>
       </c>
     </row>
-    <row r="415" spans="1:4">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>417</v>
       </c>
@@ -13180,7 +13208,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="416" spans="1:4">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>418</v>
       </c>
@@ -13194,7 +13222,7 @@
         <v>8200</v>
       </c>
     </row>
-    <row r="417" spans="1:4">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>419</v>
       </c>
@@ -13208,7 +13236,7 @@
         <v>8200</v>
       </c>
     </row>
-    <row r="418" spans="1:4">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>420</v>
       </c>
@@ -13222,7 +13250,7 @@
         <v>5748</v>
       </c>
     </row>
-    <row r="419" spans="1:4">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>421</v>
       </c>
@@ -13236,7 +13264,7 @@
         <v>7514</v>
       </c>
     </row>
-    <row r="420" spans="1:4">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>422</v>
       </c>
@@ -13250,7 +13278,7 @@
         <v>6763</v>
       </c>
     </row>
-    <row r="421" spans="1:4">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>423</v>
       </c>
@@ -13264,7 +13292,7 @@
         <v>3311</v>
       </c>
     </row>
-    <row r="422" spans="1:4">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>424</v>
       </c>
@@ -13278,7 +13306,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="423" spans="1:4">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>425</v>
       </c>
@@ -13292,7 +13320,7 @@
         <v>5947</v>
       </c>
     </row>
-    <row r="424" spans="1:4">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>426</v>
       </c>
@@ -13306,7 +13334,7 @@
         <v>6398</v>
       </c>
     </row>
-    <row r="425" spans="1:4">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>427</v>
       </c>
@@ -13320,7 +13348,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="426" spans="1:4">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>428</v>
       </c>
@@ -13334,7 +13362,7 @@
         <v>6096</v>
       </c>
     </row>
-    <row r="427" spans="1:4">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>429</v>
       </c>
@@ -13348,7 +13376,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="428" spans="1:4">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>430</v>
       </c>
@@ -13362,7 +13390,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="429" spans="1:4">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>431</v>
       </c>
@@ -13376,7 +13404,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="430" spans="1:4">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>432</v>
       </c>
@@ -13390,7 +13418,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="431" spans="1:4">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>433</v>
       </c>
@@ -13404,7 +13432,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="432" spans="1:4">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>434</v>
       </c>
@@ -13418,7 +13446,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="433" spans="1:4">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>435</v>
       </c>
@@ -13432,7 +13460,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="434" spans="1:4">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>436</v>
       </c>
@@ -13446,7 +13474,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="435" spans="1:4">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>437</v>
       </c>
@@ -13460,7 +13488,7 @@
         <v>8440</v>
       </c>
     </row>
-    <row r="436" spans="1:4">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>438</v>
       </c>
@@ -13474,7 +13502,7 @@
         <v>8440</v>
       </c>
     </row>
-    <row r="437" spans="1:4">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>439</v>
       </c>
@@ -13488,7 +13516,7 @@
         <v>8440</v>
       </c>
     </row>
-    <row r="438" spans="1:4">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>440</v>
       </c>
@@ -13502,7 +13530,7 @@
         <v>6670</v>
       </c>
     </row>
-    <row r="439" spans="1:4">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>441</v>
       </c>
@@ -13516,7 +13544,7 @@
         <v>6418</v>
       </c>
     </row>
-    <row r="440" spans="1:4">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>442</v>
       </c>
@@ -13530,7 +13558,7 @@
         <v>6018</v>
       </c>
     </row>
-    <row r="441" spans="1:4">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>443</v>
       </c>
@@ -13544,7 +13572,7 @@
         <v>6670</v>
       </c>
     </row>
-    <row r="442" spans="1:4">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>444</v>
       </c>
@@ -13558,7 +13586,7 @@
         <v>6670</v>
       </c>
     </row>
-    <row r="443" spans="1:4">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>445</v>
       </c>
@@ -13572,7 +13600,7 @@
         <v>5707</v>
       </c>
     </row>
-    <row r="444" spans="1:4">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>446</v>
       </c>
@@ -13586,7 +13614,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="445" spans="1:4">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>447</v>
       </c>
@@ -13600,7 +13628,7 @@
         <v>4770</v>
       </c>
     </row>
-    <row r="446" spans="1:4">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>448</v>
       </c>
@@ -13614,7 +13642,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="447" spans="1:4">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>449</v>
       </c>
@@ -13628,7 +13656,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="448" spans="1:4">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>450</v>
       </c>
@@ -13642,7 +13670,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="449" spans="1:4">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>451</v>
       </c>
@@ -13656,7 +13684,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="450" spans="1:4">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>452</v>
       </c>
@@ -13670,7 +13698,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="451" spans="1:4">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>453</v>
       </c>
@@ -13684,7 +13712,7 @@
         <v>9560</v>
       </c>
     </row>
-    <row r="452" spans="1:4">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>454</v>
       </c>
@@ -13698,7 +13726,7 @@
         <v>9206</v>
       </c>
     </row>
-    <row r="453" spans="1:4">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>455</v>
       </c>
@@ -13712,7 +13740,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="454" spans="1:4">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>456</v>
       </c>
@@ -13726,7 +13754,7 @@
         <v>10333</v>
       </c>
     </row>
-    <row r="455" spans="1:4">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>457</v>
       </c>
@@ -13740,7 +13768,7 @@
         <v>8400</v>
       </c>
     </row>
-    <row r="456" spans="1:4">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>458</v>
       </c>
@@ -13754,7 +13782,7 @@
         <v>8400</v>
       </c>
     </row>
-    <row r="457" spans="1:4">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>459</v>
       </c>
@@ -13768,7 +13796,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="458" spans="1:4">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>460</v>
       </c>
@@ -13782,7 +13810,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="459" spans="1:4">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>461</v>
       </c>
@@ -13796,7 +13824,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="460" spans="1:4">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>462</v>
       </c>
@@ -13810,7 +13838,7 @@
         <v>8440</v>
       </c>
     </row>
-    <row r="461" spans="1:4">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>463</v>
       </c>
@@ -13824,7 +13852,7 @@
         <v>8440</v>
       </c>
     </row>
-    <row r="462" spans="1:4">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>464</v>
       </c>
@@ -13838,7 +13866,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="463" spans="1:4">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>465</v>
       </c>
@@ -13852,7 +13880,7 @@
         <v>6325</v>
       </c>
     </row>
-    <row r="464" spans="1:4">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>466</v>
       </c>
@@ -13866,7 +13894,7 @@
         <v>2563</v>
       </c>
     </row>
-    <row r="465" spans="1:4">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>467</v>
       </c>
@@ -13880,7 +13908,7 @@
         <v>7689</v>
       </c>
     </row>
-    <row r="466" spans="1:4">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>468</v>
       </c>
@@ -13894,7 +13922,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="467" spans="1:4">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>469</v>
       </c>
@@ -13908,7 +13936,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="468" spans="1:4">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>470</v>
       </c>
@@ -13922,7 +13950,7 @@
         <v>6240</v>
       </c>
     </row>
-    <row r="469" spans="1:4">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>471</v>
       </c>
@@ -13936,7 +13964,7 @@
         <v>6570</v>
       </c>
     </row>
-    <row r="470" spans="1:4">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>472</v>
       </c>
@@ -13950,7 +13978,7 @@
         <v>6570</v>
       </c>
     </row>
-    <row r="471" spans="1:4">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>473</v>
       </c>
@@ -13964,7 +13992,7 @@
         <v>10140</v>
       </c>
     </row>
-    <row r="472" spans="1:4">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>474</v>
       </c>
@@ -13978,7 +14006,7 @@
         <v>10140</v>
       </c>
     </row>
-    <row r="473" spans="1:4">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>475</v>
       </c>
@@ -13992,7 +14020,7 @@
         <v>5209</v>
       </c>
     </row>
-    <row r="474" spans="1:4">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>476</v>
       </c>
@@ -14006,7 +14034,7 @@
         <v>5063</v>
       </c>
     </row>
-    <row r="475" spans="1:4">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>477</v>
       </c>
@@ -14020,7 +14048,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="476" spans="1:4">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>478</v>
       </c>
@@ -14034,7 +14062,7 @@
         <v>10140</v>
       </c>
     </row>
-    <row r="477" spans="1:4">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>479</v>
       </c>
@@ -14048,7 +14076,7 @@
         <v>10140</v>
       </c>
     </row>
-    <row r="478" spans="1:4">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>480</v>
       </c>
@@ -14062,7 +14090,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="479" spans="1:4">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>481</v>
       </c>
@@ -14076,7 +14104,7 @@
         <v>7360</v>
       </c>
     </row>
-    <row r="480" spans="1:4">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>482</v>
       </c>
@@ -14090,7 +14118,7 @@
         <v>7360</v>
       </c>
     </row>
-    <row r="481" spans="1:4">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>483</v>
       </c>
@@ -14104,7 +14132,7 @@
         <v>4022</v>
       </c>
     </row>
-    <row r="482" spans="1:4">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>484</v>
       </c>
@@ -14118,7 +14146,7 @@
         <v>4461</v>
       </c>
     </row>
-    <row r="483" spans="1:4">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>485</v>
       </c>
@@ -14132,7 +14160,7 @@
         <v>5343</v>
       </c>
     </row>
-    <row r="484" spans="1:4">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>486</v>
       </c>
@@ -14146,7 +14174,7 @@
         <v>5177</v>
       </c>
     </row>
-    <row r="485" spans="1:4">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>487</v>
       </c>
@@ -14160,7 +14188,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="486" spans="1:4">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>488</v>
       </c>
@@ -14174,7 +14202,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="487" spans="1:4">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>489</v>
       </c>
@@ -14188,7 +14216,7 @@
         <v>4487</v>
       </c>
     </row>
-    <row r="488" spans="1:4">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>490</v>
       </c>
@@ -14202,7 +14230,7 @@
         <v>4660</v>
       </c>
     </row>
-    <row r="489" spans="1:4">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>491</v>
       </c>
@@ -14216,7 +14244,7 @@
         <v>5540</v>
       </c>
     </row>
-    <row r="490" spans="1:4">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>492</v>
       </c>
@@ -14230,7 +14258,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="491" spans="1:4">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>493</v>
       </c>
@@ -14244,7 +14272,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="492" spans="1:4">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>494</v>
       </c>
@@ -14258,7 +14286,7 @@
         <v>9670</v>
       </c>
     </row>
-    <row r="493" spans="1:4">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>495</v>
       </c>
@@ -14272,7 +14300,7 @@
         <v>9670</v>
       </c>
     </row>
-    <row r="494" spans="1:4">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>496</v>
       </c>
@@ -14286,7 +14314,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="495" spans="1:4">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>497</v>
       </c>
@@ -14300,7 +14328,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="496" spans="1:4">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>498</v>
       </c>
@@ -14314,7 +14342,7 @@
         <v>7300</v>
       </c>
     </row>
-    <row r="497" spans="1:4">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>499</v>
       </c>
@@ -14328,7 +14356,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="498" spans="1:4">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>500</v>
       </c>
@@ -14342,7 +14370,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="499" spans="1:4">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>501</v>
       </c>
@@ -14356,7 +14384,7 @@
         <v>7650</v>
       </c>
     </row>
-    <row r="500" spans="1:4">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>502</v>
       </c>
@@ -14370,7 +14398,7 @@
         <v>6847</v>
       </c>
     </row>
-    <row r="501" spans="1:4">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>503</v>
       </c>
@@ -14384,7 +14412,7 @@
         <v>6268</v>
       </c>
     </row>
-    <row r="502" spans="1:4">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>504</v>
       </c>
@@ -14398,7 +14426,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="503" spans="1:4">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>505</v>
       </c>
@@ -14412,7 +14440,7 @@
         <v>4763</v>
       </c>
     </row>
-    <row r="504" spans="1:4">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>506</v>
       </c>
@@ -14426,7 +14454,7 @@
         <v>2556</v>
       </c>
     </row>
-    <row r="505" spans="1:4">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>507</v>
       </c>
@@ -14440,7 +14468,7 @@
         <v>4661</v>
       </c>
     </row>
-    <row r="506" spans="1:4">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>508</v>
       </c>
@@ -14454,7 +14482,7 @@
         <v>5750</v>
       </c>
     </row>
-    <row r="507" spans="1:4">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>509</v>
       </c>
@@ -14468,7 +14496,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="508" spans="1:4">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>510</v>
       </c>
@@ -14482,7 +14510,7 @@
         <v>4849</v>
       </c>
     </row>
-    <row r="509" spans="1:4">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>511</v>
       </c>
@@ -14496,7 +14524,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="510" spans="1:4">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>512</v>
       </c>
@@ -14510,7 +14538,7 @@
         <v>4956</v>
       </c>
     </row>
-    <row r="511" spans="1:4">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>513</v>
       </c>
@@ -14524,7 +14552,7 @@
         <v>4211</v>
       </c>
     </row>
-    <row r="512" spans="1:4">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>514</v>
       </c>
@@ -14538,7 +14566,7 @@
         <v>13831</v>
       </c>
     </row>
-    <row r="513" spans="1:4">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>515</v>
       </c>
@@ -14552,7 +14580,7 @@
         <v>6700</v>
       </c>
     </row>
-    <row r="514" spans="1:4">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>516</v>
       </c>
@@ -14566,7 +14594,7 @@
         <v>6700</v>
       </c>
     </row>
-    <row r="515" spans="1:4">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>517</v>
       </c>
@@ -14580,7 +14608,7 @@
         <v>5087</v>
       </c>
     </row>
-    <row r="516" spans="1:4">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>518</v>
       </c>
@@ -14594,7 +14622,7 @@
         <v>5131</v>
       </c>
     </row>
-    <row r="517" spans="1:4">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>519</v>
       </c>
@@ -14608,7 +14636,7 @@
         <v>5127</v>
       </c>
     </row>
-    <row r="518" spans="1:4">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>520</v>
       </c>
@@ -14622,7 +14650,7 @@
         <v>3880</v>
       </c>
     </row>
-    <row r="519" spans="1:4">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>521</v>
       </c>
@@ -14636,7 +14664,7 @@
         <v>5234</v>
       </c>
     </row>
-    <row r="520" spans="1:4">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>522</v>
       </c>
@@ -14650,7 +14678,7 @@
         <v>4859</v>
       </c>
     </row>
-    <row r="521" spans="1:4">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>523</v>
       </c>
@@ -14664,7 +14692,7 @@
         <v>4807</v>
       </c>
     </row>
-    <row r="522" spans="1:4">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>524</v>
       </c>
@@ -14678,7 +14706,7 @@
         <v>5234</v>
       </c>
     </row>
-    <row r="523" spans="1:4">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>525</v>
       </c>
@@ -14692,7 +14720,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="524" spans="1:4">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>526</v>
       </c>
@@ -14706,7 +14734,7 @@
         <v>4867</v>
       </c>
     </row>
-    <row r="525" spans="1:4">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>527</v>
       </c>
@@ -14720,7 +14748,7 @@
         <v>5234</v>
       </c>
     </row>
-    <row r="526" spans="1:4">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>528</v>
       </c>
@@ -14734,7 +14762,7 @@
         <v>10140</v>
       </c>
     </row>
-    <row r="527" spans="1:4">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>529</v>
       </c>
@@ -14748,7 +14776,7 @@
         <v>5215</v>
       </c>
     </row>
-    <row r="528" spans="1:4">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>530</v>
       </c>
@@ -14762,7 +14790,7 @@
         <v>5152</v>
       </c>
     </row>
-    <row r="529" spans="1:4">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>531</v>
       </c>
@@ -14776,7 +14804,7 @@
         <v>5128</v>
       </c>
     </row>
-    <row r="530" spans="1:4">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>532</v>
       </c>
@@ -14790,7 +14818,7 @@
         <v>5036</v>
       </c>
     </row>
-    <row r="531" spans="1:4">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>533</v>
       </c>
@@ -14804,7 +14832,7 @@
         <v>4857</v>
       </c>
     </row>
-    <row r="532" spans="1:4">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>534</v>
       </c>
@@ -14818,7 +14846,7 @@
         <v>4875</v>
       </c>
     </row>
-    <row r="533" spans="1:4">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>535</v>
       </c>
@@ -14832,7 +14860,7 @@
         <v>10140</v>
       </c>
     </row>
-    <row r="534" spans="1:4">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>536</v>
       </c>
@@ -14846,7 +14874,7 @@
         <v>10140</v>
       </c>
     </row>
-    <row r="535" spans="1:4">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
         <v>537</v>
       </c>
@@ -14860,7 +14888,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="536" spans="1:4">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
         <v>538</v>
       </c>
@@ -14874,7 +14902,7 @@
         <v>11999</v>
       </c>
     </row>
-    <row r="537" spans="1:4">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
         <v>539</v>
       </c>
@@ -14888,7 +14916,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="538" spans="1:4">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
         <v>540</v>
       </c>
@@ -14902,7 +14930,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="539" spans="1:4">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
         <v>541</v>
       </c>
@@ -14916,7 +14944,7 @@
         <v>5837</v>
       </c>
     </row>
-    <row r="540" spans="1:4">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
         <v>542</v>
       </c>
@@ -14930,7 +14958,7 @@
         <v>13149</v>
       </c>
     </row>
-    <row r="541" spans="1:4">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
         <v>543</v>
       </c>
@@ -14944,7 +14972,7 @@
         <v>5779</v>
       </c>
     </row>
-    <row r="542" spans="1:4">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
         <v>544</v>
       </c>
@@ -14958,7 +14986,7 @@
         <v>6353</v>
       </c>
     </row>
-    <row r="543" spans="1:4">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>545</v>
       </c>
@@ -14972,7 +15000,7 @@
         <v>10400</v>
       </c>
     </row>
-    <row r="544" spans="1:4">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
         <v>546</v>
       </c>
@@ -14986,7 +15014,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="545" spans="1:4">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
         <v>547</v>
       </c>
@@ -15000,7 +15028,7 @@
         <v>8079</v>
       </c>
     </row>
-    <row r="546" spans="1:4">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
         <v>548</v>
       </c>
@@ -15014,7 +15042,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="547" spans="1:4">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
         <v>549</v>
       </c>
@@ -15028,7 +15056,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="548" spans="1:4">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
         <v>550</v>
       </c>
@@ -15042,7 +15070,7 @@
         <v>10026</v>
       </c>
     </row>
-    <row r="549" spans="1:4">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
         <v>551</v>
       </c>
@@ -15056,7 +15084,7 @@
         <v>8079</v>
       </c>
     </row>
-    <row r="550" spans="1:4">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
         <v>552</v>
       </c>
@@ -15070,7 +15098,7 @@
         <v>10026</v>
       </c>
     </row>
-    <row r="551" spans="1:4">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>553</v>
       </c>
@@ -15084,7 +15112,7 @@
         <v>5943</v>
       </c>
     </row>
-    <row r="552" spans="1:4">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
         <v>554</v>
       </c>
@@ -15098,7 +15126,7 @@
         <v>5813</v>
       </c>
     </row>
-    <row r="553" spans="1:4">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>555</v>
       </c>
@@ -15112,7 +15140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:4">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>556</v>
       </c>
@@ -15126,7 +15154,7 @@
         <v>4760</v>
       </c>
     </row>
-    <row r="555" spans="1:4">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
         <v>557</v>
       </c>
@@ -15140,7 +15168,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="556" spans="1:4">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
         <v>558</v>
       </c>
@@ -15154,7 +15182,7 @@
         <v>5310</v>
       </c>
     </row>
-    <row r="557" spans="1:4">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>559</v>
       </c>
@@ -15168,7 +15196,7 @@
         <v>4474</v>
       </c>
     </row>
-    <row r="558" spans="1:4">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
         <v>560</v>
       </c>
@@ -15182,7 +15210,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="559" spans="1:4">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>561</v>
       </c>
@@ -15196,7 +15224,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="560" spans="1:4">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
         <v>562</v>
       </c>
@@ -15210,7 +15238,7 @@
         <v>4840</v>
       </c>
     </row>
-    <row r="561" spans="1:4">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>563</v>
       </c>
@@ -15224,7 +15252,7 @@
         <v>4840</v>
       </c>
     </row>
-    <row r="562" spans="1:4">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>564</v>
       </c>
@@ -15238,7 +15266,7 @@
         <v>4337</v>
       </c>
     </row>
-    <row r="563" spans="1:4">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>565</v>
       </c>
@@ -15252,7 +15280,7 @@
         <v>4772</v>
       </c>
     </row>
-    <row r="564" spans="1:4">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>566</v>
       </c>
@@ -15266,7 +15294,7 @@
         <v>4260</v>
       </c>
     </row>
-    <row r="565" spans="1:4">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>567</v>
       </c>
@@ -15280,7 +15308,7 @@
         <v>4160</v>
       </c>
     </row>
-    <row r="566" spans="1:4">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>568</v>
       </c>
@@ -15294,7 +15322,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="567" spans="1:4">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>569</v>
       </c>
@@ -15308,7 +15336,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="568" spans="1:4">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>570</v>
       </c>
@@ -15322,7 +15350,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="569" spans="1:4">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>571</v>
       </c>
@@ -15336,7 +15364,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="570" spans="1:4">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
         <v>572</v>
       </c>
@@ -15350,7 +15378,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="571" spans="1:4">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
         <v>573</v>
       </c>
@@ -15364,7 +15392,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="572" spans="1:4">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
         <v>574</v>
       </c>
@@ -15378,7 +15406,7 @@
         <v>5160</v>
       </c>
     </row>
-    <row r="573" spans="1:4">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
         <v>575</v>
       </c>
@@ -15392,7 +15420,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="574" spans="1:4">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>576</v>
       </c>
@@ -15406,7 +15434,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="575" spans="1:4">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>577</v>
       </c>
@@ -15420,7 +15448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:4">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>578</v>
       </c>
@@ -15434,7 +15462,7 @@
         <v>7626</v>
       </c>
     </row>
-    <row r="577" spans="1:4">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>579</v>
       </c>
@@ -15448,7 +15476,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="578" spans="1:4">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
         <v>580</v>
       </c>
@@ -15462,7 +15490,7 @@
         <v>6596</v>
       </c>
     </row>
-    <row r="579" spans="1:4">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>581</v>
       </c>
@@ -15476,7 +15504,7 @@
         <v>6545</v>
       </c>
     </row>
-    <row r="580" spans="1:4">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
         <v>582</v>
       </c>
@@ -15490,7 +15518,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="581" spans="1:4">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
         <v>583</v>
       </c>
@@ -15504,7 +15532,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="582" spans="1:4">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
         <v>584</v>
       </c>
@@ -15518,7 +15546,7 @@
         <v>3734</v>
       </c>
     </row>
-    <row r="583" spans="1:4">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
         <v>585</v>
       </c>
@@ -15532,7 +15560,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="584" spans="1:4">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
         <v>586</v>
       </c>
@@ -15546,7 +15574,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="585" spans="1:4">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
         <v>587</v>
       </c>
@@ -15560,7 +15588,7 @@
         <v>3672</v>
       </c>
     </row>
-    <row r="586" spans="1:4">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>588</v>
       </c>
@@ -15574,7 +15602,7 @@
         <v>10239</v>
       </c>
     </row>
-    <row r="587" spans="1:4">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>589</v>
       </c>
@@ -15588,7 +15616,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="588" spans="1:4">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>590</v>
       </c>
@@ -15602,7 +15630,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="589" spans="1:4">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>591</v>
       </c>
@@ -15616,7 +15644,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="590" spans="1:4">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>592</v>
       </c>
@@ -15630,7 +15658,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="591" spans="1:4">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
         <v>593</v>
       </c>
@@ -15644,7 +15672,7 @@
         <v>7080</v>
       </c>
     </row>
-    <row r="592" spans="1:4">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
         <v>594</v>
       </c>
@@ -15658,7 +15686,7 @@
         <v>5770</v>
       </c>
     </row>
-    <row r="593" spans="1:4">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
         <v>595</v>
       </c>
@@ -15672,7 +15700,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="594" spans="1:4">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
         <v>596</v>
       </c>
@@ -15686,7 +15714,7 @@
         <v>3840</v>
       </c>
     </row>
-    <row r="595" spans="1:4">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
         <v>597</v>
       </c>
@@ -15700,7 +15728,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="596" spans="1:4">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
         <v>598</v>
       </c>
@@ -15714,7 +15742,7 @@
         <v>3442</v>
       </c>
     </row>
-    <row r="597" spans="1:4">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
         <v>599</v>
       </c>
@@ -15728,7 +15756,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="598" spans="1:4">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>600</v>
       </c>
@@ -15742,7 +15770,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="599" spans="1:4">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>601</v>
       </c>
@@ -15756,7 +15784,7 @@
         <v>6013</v>
       </c>
     </row>
-    <row r="600" spans="1:4">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>602</v>
       </c>
@@ -15770,7 +15798,7 @@
         <v>6750</v>
       </c>
     </row>
-    <row r="601" spans="1:4">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
         <v>603</v>
       </c>
@@ -15784,7 +15812,7 @@
         <v>6488</v>
       </c>
     </row>
-    <row r="602" spans="1:4">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
         <v>604</v>
       </c>
@@ -15798,7 +15826,7 @@
         <v>6599</v>
       </c>
     </row>
-    <row r="603" spans="1:4">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>605</v>
       </c>
@@ -15812,7 +15840,7 @@
         <v>6696</v>
       </c>
     </row>
-    <row r="604" spans="1:4">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>606</v>
       </c>
@@ -15826,7 +15854,7 @@
         <v>6942</v>
       </c>
     </row>
-    <row r="605" spans="1:4">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
         <v>607</v>
       </c>
@@ -15840,7 +15868,7 @@
         <v>6350</v>
       </c>
     </row>
-    <row r="606" spans="1:4">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
         <v>608</v>
       </c>
@@ -15854,7 +15882,7 @@
         <v>6350</v>
       </c>
     </row>
-    <row r="607" spans="1:4">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>609</v>
       </c>
@@ -15868,7 +15896,7 @@
         <v>6350</v>
       </c>
     </row>
-    <row r="608" spans="1:4">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>610</v>
       </c>
@@ -15882,7 +15910,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="609" spans="1:4">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
         <v>611</v>
       </c>
@@ -15896,7 +15924,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="610" spans="1:4">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
         <v>612</v>
       </c>
@@ -15910,7 +15938,7 @@
         <v>10800</v>
       </c>
     </row>
-    <row r="611" spans="1:4">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
         <v>613</v>
       </c>
@@ -15924,7 +15952,7 @@
         <v>9970</v>
       </c>
     </row>
-    <row r="612" spans="1:4">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
         <v>614</v>
       </c>
@@ -15938,7 +15966,7 @@
         <v>7287</v>
       </c>
     </row>
-    <row r="613" spans="1:4">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
         <v>615</v>
       </c>
@@ -15952,7 +15980,7 @@
         <v>4960</v>
       </c>
     </row>
-    <row r="614" spans="1:4">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
         <v>616</v>
       </c>
@@ -15966,7 +15994,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="615" spans="1:4">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
         <v>617</v>
       </c>
@@ -15980,7 +16008,7 @@
         <v>4010</v>
       </c>
     </row>
-    <row r="616" spans="1:4">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
         <v>618</v>
       </c>
@@ -15994,7 +16022,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="617" spans="1:4">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
         <v>619</v>
       </c>
@@ -16008,7 +16036,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="618" spans="1:4">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
         <v>620</v>
       </c>
@@ -16022,7 +16050,7 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="619" spans="1:4">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
         <v>621</v>
       </c>
@@ -16036,7 +16064,7 @@
         <v>5892</v>
       </c>
     </row>
-    <row r="620" spans="1:4">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
         <v>622</v>
       </c>
@@ -16050,7 +16078,7 @@
         <v>4720</v>
       </c>
     </row>
-    <row r="621" spans="1:4">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
         <v>623</v>
       </c>
@@ -16064,7 +16092,7 @@
         <v>4193</v>
       </c>
     </row>
-    <row r="622" spans="1:4">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
         <v>624</v>
       </c>
@@ -16078,7 +16106,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="623" spans="1:4">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
         <v>625</v>
       </c>
@@ -16092,7 +16120,7 @@
         <v>8222</v>
       </c>
     </row>
-    <row r="624" spans="1:4">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
         <v>626</v>
       </c>
@@ -16106,7 +16134,7 @@
         <v>4353</v>
       </c>
     </row>
-    <row r="625" spans="1:4">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
         <v>627</v>
       </c>
@@ -16120,7 +16148,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="626" spans="1:4">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
         <v>628</v>
       </c>
@@ -16134,7 +16162,7 @@
         <v>7918</v>
       </c>
     </row>
-    <row r="627" spans="1:4">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
         <v>629</v>
       </c>
@@ -16148,7 +16176,7 @@
         <v>4380</v>
       </c>
     </row>
-    <row r="628" spans="1:4">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
         <v>630</v>
       </c>
@@ -16162,7 +16190,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="629" spans="1:4">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
         <v>631</v>
       </c>
@@ -16176,7 +16204,7 @@
         <v>5030</v>
       </c>
     </row>
-    <row r="630" spans="1:4">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
         <v>632</v>
       </c>
@@ -16190,7 +16218,7 @@
         <v>4280</v>
       </c>
     </row>
-    <row r="631" spans="1:4">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
         <v>633</v>
       </c>
@@ -16204,7 +16232,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="632" spans="1:4">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
         <v>634</v>
       </c>
@@ -16218,7 +16246,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="633" spans="1:4">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
         <v>635</v>
       </c>
@@ -16232,7 +16260,7 @@
         <v>4160</v>
       </c>
     </row>
-    <row r="634" spans="1:4">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
         <v>636</v>
       </c>
@@ -16246,7 +16274,7 @@
         <v>3960</v>
       </c>
     </row>
-    <row r="635" spans="1:4">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
         <v>637</v>
       </c>
@@ -16260,7 +16288,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="636" spans="1:4">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
         <v>638</v>
       </c>
@@ -16274,7 +16302,7 @@
         <v>4604</v>
       </c>
     </row>
-    <row r="637" spans="1:4">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
         <v>639</v>
       </c>
@@ -16288,7 +16316,7 @@
         <v>4704</v>
       </c>
     </row>
-    <row r="638" spans="1:4">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
         <v>640</v>
       </c>
@@ -16302,7 +16330,7 @@
         <v>4704</v>
       </c>
     </row>
-    <row r="639" spans="1:4">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
         <v>641</v>
       </c>
@@ -16316,7 +16344,7 @@
         <v>11687</v>
       </c>
     </row>
-    <row r="640" spans="1:4">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
         <v>642</v>
       </c>
@@ -16330,7 +16358,7 @@
         <v>6223</v>
       </c>
     </row>
-    <row r="641" spans="1:4">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
         <v>643</v>
       </c>
@@ -16344,7 +16372,7 @@
         <v>9516</v>
       </c>
     </row>
-    <row r="642" spans="1:4">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
         <v>644</v>
       </c>
@@ -16358,7 +16386,7 @@
         <v>4280</v>
       </c>
     </row>
-    <row r="643" spans="1:4">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
         <v>645</v>
       </c>
@@ -16372,7 +16400,7 @@
         <v>9580</v>
       </c>
     </row>
-    <row r="644" spans="1:4">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
         <v>646</v>
       </c>
@@ -16386,7 +16414,7 @@
         <v>6347</v>
       </c>
     </row>
-    <row r="645" spans="1:4">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
         <v>647</v>
       </c>
@@ -16400,7 +16428,7 @@
         <v>3952</v>
       </c>
     </row>
-    <row r="646" spans="1:4">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
         <v>648</v>
       </c>
@@ -16414,7 +16442,7 @@
         <v>4993</v>
       </c>
     </row>
-    <row r="647" spans="1:4">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
         <v>649</v>
       </c>
@@ -16428,7 +16456,7 @@
         <v>3460</v>
       </c>
     </row>
-    <row r="648" spans="1:4">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
         <v>650</v>
       </c>
@@ -16442,7 +16470,7 @@
         <v>3460</v>
       </c>
     </row>
-    <row r="649" spans="1:4">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
         <v>651</v>
       </c>
@@ -16456,7 +16484,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="650" spans="1:4">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
         <v>652</v>
       </c>
@@ -16470,7 +16498,7 @@
         <v>8329</v>
       </c>
     </row>
-    <row r="651" spans="1:4">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
         <v>653</v>
       </c>
@@ -16484,7 +16512,7 @@
         <v>9150</v>
       </c>
     </row>
-    <row r="652" spans="1:4">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
         <v>654</v>
       </c>
@@ -16498,7 +16526,7 @@
         <v>8363</v>
       </c>
     </row>
-    <row r="653" spans="1:4">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
         <v>655</v>
       </c>
@@ -16512,7 +16540,7 @@
         <v>8363</v>
       </c>
     </row>
-    <row r="654" spans="1:4">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
         <v>656</v>
       </c>
@@ -16526,7 +16554,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="655" spans="1:4">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
         <v>657</v>
       </c>
@@ -16540,7 +16568,7 @@
         <v>4070</v>
       </c>
     </row>
-    <row r="656" spans="1:4">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
         <v>658</v>
       </c>
@@ -16554,7 +16582,7 @@
         <v>7137</v>
       </c>
     </row>
-    <row r="657" spans="1:4">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
         <v>659</v>
       </c>
@@ -16568,7 +16596,7 @@
         <v>3595</v>
       </c>
     </row>
-    <row r="658" spans="1:4">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
         <v>660</v>
       </c>
@@ -16582,7 +16610,7 @@
         <v>6840</v>
       </c>
     </row>
-    <row r="659" spans="1:4">
+    <row r="659" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
         <v>661</v>
       </c>
@@ -16596,7 +16624,7 @@
         <v>6756</v>
       </c>
     </row>
-    <row r="660" spans="1:4">
+    <row r="660" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
         <v>662</v>
       </c>
@@ -16610,7 +16638,7 @@
         <v>7138</v>
       </c>
     </row>
-    <row r="661" spans="1:4">
+    <row r="661" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A661" t="s">
         <v>663</v>
       </c>
@@ -16624,7 +16652,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="662" spans="1:4">
+    <row r="662" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
         <v>664</v>
       </c>
@@ -16638,7 +16666,7 @@
         <v>2892</v>
       </c>
     </row>
-    <row r="663" spans="1:4">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A663" t="s">
         <v>665</v>
       </c>
@@ -16652,7 +16680,7 @@
         <v>5676</v>
       </c>
     </row>
-    <row r="664" spans="1:4">
+    <row r="664" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
         <v>666</v>
       </c>
@@ -16666,7 +16694,7 @@
         <v>7398</v>
       </c>
     </row>
-    <row r="665" spans="1:4">
+    <row r="665" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A665" t="s">
         <v>667</v>
       </c>
@@ -16680,7 +16708,7 @@
         <v>7253</v>
       </c>
     </row>
-    <row r="666" spans="1:4">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A666" t="s">
         <v>668</v>
       </c>
@@ -16694,7 +16722,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="667" spans="1:4">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A667" t="s">
         <v>669</v>
       </c>
@@ -16708,7 +16736,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="668" spans="1:4">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A668" t="s">
         <v>670</v>
       </c>
@@ -16722,7 +16750,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="669" spans="1:4">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A669" t="s">
         <v>671</v>
       </c>
@@ -16736,7 +16764,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="670" spans="1:4">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A670" t="s">
         <v>672</v>
       </c>
@@ -16750,7 +16778,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="671" spans="1:4">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A671" t="s">
         <v>673</v>
       </c>
@@ -16764,7 +16792,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="672" spans="1:4">
+    <row r="672" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A672" t="s">
         <v>674</v>
       </c>
@@ -16778,7 +16806,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="673" spans="1:4">
+    <row r="673" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A673" t="s">
         <v>675</v>
       </c>
@@ -16792,7 +16820,7 @@
         <v>5550</v>
       </c>
     </row>
-    <row r="674" spans="1:4">
+    <row r="674" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A674" t="s">
         <v>676</v>
       </c>
@@ -16806,7 +16834,7 @@
         <v>24529</v>
       </c>
     </row>
-    <row r="675" spans="1:4">
+    <row r="675" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A675" t="s">
         <v>677</v>
       </c>
@@ -16820,7 +16848,7 @@
         <v>19620</v>
       </c>
     </row>
-    <row r="676" spans="1:4">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A676" t="s">
         <v>678</v>
       </c>
@@ -16834,7 +16862,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="677" spans="1:4">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A677" t="s">
         <v>679</v>
       </c>
@@ -16848,7 +16876,7 @@
         <v>6175</v>
       </c>
     </row>
-    <row r="678" spans="1:4">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A678" t="s">
         <v>680</v>
       </c>
@@ -16862,7 +16890,7 @@
         <v>9310</v>
       </c>
     </row>
-    <row r="679" spans="1:4">
+    <row r="679" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A679" t="s">
         <v>681</v>
       </c>
@@ -16876,7 +16904,7 @@
         <v>9620</v>
       </c>
     </row>
-    <row r="680" spans="1:4">
+    <row r="680" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A680" t="s">
         <v>682</v>
       </c>
@@ -16890,7 +16918,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="681" spans="1:4">
+    <row r="681" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A681" t="s">
         <v>683</v>
       </c>
@@ -16904,7 +16932,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="682" spans="1:4">
+    <row r="682" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A682" t="s">
         <v>684</v>
       </c>
@@ -16918,7 +16946,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="683" spans="1:4">
+    <row r="683" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A683" t="s">
         <v>685</v>
       </c>
@@ -16932,7 +16960,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="684" spans="1:4">
+    <row r="684" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A684" t="s">
         <v>686</v>
       </c>
@@ -16946,7 +16974,7 @@
         <v>4868</v>
       </c>
     </row>
-    <row r="685" spans="1:4">
+    <row r="685" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A685" t="s">
         <v>687</v>
       </c>
@@ -16960,7 +16988,7 @@
         <v>4868</v>
       </c>
     </row>
-    <row r="686" spans="1:4">
+    <row r="686" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A686" t="s">
         <v>688</v>
       </c>
@@ -16974,7 +17002,7 @@
         <v>2921</v>
       </c>
     </row>
-    <row r="687" spans="1:4">
+    <row r="687" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A687" t="s">
         <v>689</v>
       </c>
@@ -16988,7 +17016,7 @@
         <v>2921</v>
       </c>
     </row>
-    <row r="688" spans="1:4">
+    <row r="688" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A688" t="s">
         <v>690</v>
       </c>
@@ -17002,7 +17030,7 @@
         <v>4868</v>
       </c>
     </row>
-    <row r="689" spans="1:4">
+    <row r="689" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A689" t="s">
         <v>691</v>
       </c>
@@ -17016,7 +17044,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="690" spans="1:4">
+    <row r="690" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A690" t="s">
         <v>692</v>
       </c>
@@ -17030,7 +17058,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="691" spans="1:4">
+    <row r="691" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A691" t="s">
         <v>693</v>
       </c>
@@ -17044,7 +17072,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="692" spans="1:4">
+    <row r="692" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A692" t="s">
         <v>694</v>
       </c>
@@ -17058,7 +17086,7 @@
         <v>6423</v>
       </c>
     </row>
-    <row r="693" spans="1:4">
+    <row r="693" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A693" t="s">
         <v>695</v>
       </c>
@@ -17072,7 +17100,7 @@
         <v>6423</v>
       </c>
     </row>
-    <row r="694" spans="1:4">
+    <row r="694" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A694" t="s">
         <v>696</v>
       </c>
@@ -17086,7 +17114,7 @@
         <v>6423</v>
       </c>
     </row>
-    <row r="695" spans="1:4">
+    <row r="695" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A695" t="s">
         <v>697</v>
       </c>
@@ -17100,7 +17128,7 @@
         <v>5780</v>
       </c>
     </row>
-    <row r="696" spans="1:4">
+    <row r="696" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A696" t="s">
         <v>698</v>
       </c>
@@ -17114,7 +17142,7 @@
         <v>5780</v>
       </c>
     </row>
-    <row r="697" spans="1:4">
+    <row r="697" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A697" t="s">
         <v>699</v>
       </c>
@@ -17128,7 +17156,7 @@
         <v>5780</v>
       </c>
     </row>
-    <row r="698" spans="1:4">
+    <row r="698" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A698" t="s">
         <v>700</v>
       </c>
@@ -17142,7 +17170,7 @@
         <v>4850</v>
       </c>
     </row>
-    <row r="699" spans="1:4">
+    <row r="699" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A699" t="s">
         <v>701</v>
       </c>
@@ -17156,7 +17184,7 @@
         <v>4850</v>
       </c>
     </row>
-    <row r="700" spans="1:4">
+    <row r="700" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A700" t="s">
         <v>702</v>
       </c>
@@ -17170,7 +17198,7 @@
         <v>4850</v>
       </c>
     </row>
-    <row r="701" spans="1:4">
+    <row r="701" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A701" t="s">
         <v>703</v>
       </c>
@@ -17184,7 +17212,7 @@
         <v>4850</v>
       </c>
     </row>
-    <row r="702" spans="1:4">
+    <row r="702" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A702" t="s">
         <v>704</v>
       </c>
@@ -17198,7 +17226,7 @@
         <v>4693</v>
       </c>
     </row>
-    <row r="703" spans="1:4">
+    <row r="703" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A703" t="s">
         <v>705</v>
       </c>
@@ -17212,7 +17240,7 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="704" spans="1:4">
+    <row r="704" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A704" t="s">
         <v>706</v>
       </c>
@@ -17226,7 +17254,7 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="705" spans="1:4">
+    <row r="705" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A705" t="s">
         <v>707</v>
       </c>
@@ -17240,7 +17268,7 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="706" spans="1:4">
+    <row r="706" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A706" t="s">
         <v>708</v>
       </c>
@@ -17254,7 +17282,7 @@
         <v>5660</v>
       </c>
     </row>
-    <row r="707" spans="1:4">
+    <row r="707" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A707" t="s">
         <v>709</v>
       </c>
@@ -17268,7 +17296,7 @@
         <v>5660</v>
       </c>
     </row>
-    <row r="708" spans="1:4">
+    <row r="708" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A708" t="s">
         <v>710</v>
       </c>
@@ -17282,7 +17310,7 @@
         <v>5660</v>
       </c>
     </row>
-    <row r="709" spans="1:4">
+    <row r="709" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A709" t="s">
         <v>711</v>
       </c>
@@ -17296,7 +17324,7 @@
         <v>7760</v>
       </c>
     </row>
-    <row r="710" spans="1:4">
+    <row r="710" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A710" t="s">
         <v>712</v>
       </c>
@@ -17310,7 +17338,7 @@
         <v>7560</v>
       </c>
     </row>
-    <row r="711" spans="1:4">
+    <row r="711" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A711" t="s">
         <v>713</v>
       </c>
@@ -17324,7 +17352,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="712" spans="1:4">
+    <row r="712" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A712" t="s">
         <v>714</v>
       </c>
@@ -17338,7 +17366,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="713" spans="1:4">
+    <row r="713" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A713" t="s">
         <v>715</v>
       </c>
@@ -17352,7 +17380,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="714" spans="1:4">
+    <row r="714" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A714" t="s">
         <v>716</v>
       </c>
@@ -17366,7 +17394,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="715" spans="1:4">
+    <row r="715" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A715" t="s">
         <v>717</v>
       </c>
@@ -17380,7 +17408,7 @@
         <v>4904</v>
       </c>
     </row>
-    <row r="716" spans="1:4">
+    <row r="716" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A716" t="s">
         <v>718</v>
       </c>
@@ -17394,7 +17422,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="717" spans="1:4">
+    <row r="717" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A717" t="s">
         <v>719</v>
       </c>
@@ -17408,7 +17436,7 @@
         <v>13740</v>
       </c>
     </row>
-    <row r="718" spans="1:4">
+    <row r="718" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A718" t="s">
         <v>720</v>
       </c>
@@ -17422,7 +17450,7 @@
         <v>17770</v>
       </c>
     </row>
-    <row r="719" spans="1:4">
+    <row r="719" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A719" t="s">
         <v>721</v>
       </c>
@@ -17436,7 +17464,7 @@
         <v>14570</v>
       </c>
     </row>
-    <row r="720" spans="1:4">
+    <row r="720" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A720" t="s">
         <v>722</v>
       </c>
@@ -17450,7 +17478,7 @@
         <v>18590</v>
       </c>
     </row>
-    <row r="721" spans="1:4">
+    <row r="721" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A721" t="s">
         <v>723</v>
       </c>
@@ -17464,7 +17492,7 @@
         <v>29950</v>
       </c>
     </row>
-    <row r="722" spans="1:4">
+    <row r="722" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A722" t="s">
         <v>724</v>
       </c>
@@ -17478,7 +17506,7 @@
         <v>3860</v>
       </c>
     </row>
-    <row r="723" spans="1:4">
+    <row r="723" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A723" t="s">
         <v>725</v>
       </c>
@@ -17492,7 +17520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:4">
+    <row r="724" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A724" t="s">
         <v>726</v>
       </c>
@@ -17506,7 +17534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:4">
+    <row r="725" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A725" t="s">
         <v>727</v>
       </c>
@@ -17520,7 +17548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:4">
+    <row r="726" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A726" t="s">
         <v>728</v>
       </c>
@@ -17534,7 +17562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:4">
+    <row r="727" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A727" t="s">
         <v>729</v>
       </c>
@@ -17548,7 +17576,7 @@
         <v>8690</v>
       </c>
     </row>
-    <row r="728" spans="1:4">
+    <row r="728" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A728" t="s">
         <v>730</v>
       </c>
@@ -17562,7 +17590,7 @@
         <v>8250</v>
       </c>
     </row>
-    <row r="729" spans="1:4">
+    <row r="729" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A729" t="s">
         <v>731</v>
       </c>
@@ -17576,7 +17604,7 @@
         <v>5115</v>
       </c>
     </row>
-    <row r="730" spans="1:4">
+    <row r="730" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A730" t="s">
         <v>732</v>
       </c>
@@ -17590,7 +17618,7 @@
         <v>5115</v>
       </c>
     </row>
-    <row r="731" spans="1:4">
+    <row r="731" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A731" t="s">
         <v>733</v>
       </c>
@@ -17604,7 +17632,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="732" spans="1:4">
+    <row r="732" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A732" t="s">
         <v>734</v>
       </c>
@@ -17618,7 +17646,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="733" spans="1:4">
+    <row r="733" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A733" t="s">
         <v>735</v>
       </c>
@@ -17632,7 +17660,7 @@
         <v>6070</v>
       </c>
     </row>
-    <row r="734" spans="1:4">
+    <row r="734" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A734" t="s">
         <v>736</v>
       </c>
@@ -17646,7 +17674,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="735" spans="1:4">
+    <row r="735" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A735" t="s">
         <v>737</v>
       </c>
@@ -17660,7 +17688,7 @@
         <v>10909</v>
       </c>
     </row>
-    <row r="736" spans="1:4">
+    <row r="736" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A736" t="s">
         <v>738</v>
       </c>
@@ -17674,7 +17702,7 @@
         <v>6900</v>
       </c>
     </row>
-    <row r="737" spans="1:4">
+    <row r="737" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A737" t="s">
         <v>739</v>
       </c>
@@ -17688,7 +17716,7 @@
         <v>18680</v>
       </c>
     </row>
-    <row r="738" spans="1:4">
+    <row r="738" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A738" t="s">
         <v>740</v>
       </c>
@@ -17702,7 +17730,7 @@
         <v>14180</v>
       </c>
     </row>
-    <row r="739" spans="1:4">
+    <row r="739" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A739" t="s">
         <v>741</v>
       </c>
@@ -17716,7 +17744,7 @@
         <v>6070</v>
       </c>
     </row>
-    <row r="740" spans="1:4">
+    <row r="740" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A740" t="s">
         <v>742</v>
       </c>
@@ -17730,7 +17758,7 @@
         <v>13470</v>
       </c>
     </row>
-    <row r="741" spans="1:4">
+    <row r="741" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A741" t="s">
         <v>743</v>
       </c>
@@ -17744,7 +17772,7 @@
         <v>6820</v>
       </c>
     </row>
-    <row r="742" spans="1:4">
+    <row r="742" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A742" t="s">
         <v>744</v>
       </c>
@@ -17758,7 +17786,7 @@
         <v>6140</v>
       </c>
     </row>
-    <row r="743" spans="1:4">
+    <row r="743" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A743" t="s">
         <v>745</v>
       </c>
@@ -17772,7 +17800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:4">
+    <row r="744" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A744" t="s">
         <v>746</v>
       </c>
@@ -17786,7 +17814,7 @@
         <v>7470</v>
       </c>
     </row>
-    <row r="745" spans="1:4">
+    <row r="745" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A745" t="s">
         <v>747</v>
       </c>
@@ -17800,7 +17828,7 @@
         <v>7540</v>
       </c>
     </row>
-    <row r="746" spans="1:4">
+    <row r="746" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A746" t="s">
         <v>748</v>
       </c>
@@ -17814,7 +17842,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="747" spans="1:4">
+    <row r="747" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A747" t="s">
         <v>749</v>
       </c>
@@ -17828,7 +17856,7 @@
         <v>8660</v>
       </c>
     </row>
-    <row r="748" spans="1:4">
+    <row r="748" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A748" t="s">
         <v>750</v>
       </c>
@@ -17842,7 +17870,7 @@
         <v>4631</v>
       </c>
     </row>
-    <row r="749" spans="1:4">
+    <row r="749" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A749" t="s">
         <v>751</v>
       </c>
@@ -17856,7 +17884,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="750" spans="1:4">
+    <row r="750" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A750" t="s">
         <v>752</v>
       </c>
@@ -17870,7 +17898,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="751" spans="1:4">
+    <row r="751" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A751" t="s">
         <v>753</v>
       </c>
@@ -17884,7 +17912,7 @@
         <v>9370</v>
       </c>
     </row>
-    <row r="752" spans="1:4">
+    <row r="752" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A752" t="s">
         <v>754</v>
       </c>
@@ -17898,7 +17926,7 @@
         <v>12300</v>
       </c>
     </row>
-    <row r="753" spans="1:4">
+    <row r="753" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A753" t="s">
         <v>755</v>
       </c>
@@ -17912,7 +17940,7 @@
         <v>5260</v>
       </c>
     </row>
-    <row r="754" spans="1:4">
+    <row r="754" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A754" t="s">
         <v>756</v>
       </c>
@@ -17926,7 +17954,7 @@
         <v>9230</v>
       </c>
     </row>
-    <row r="755" spans="1:4">
+    <row r="755" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A755" t="s">
         <v>757</v>
       </c>
@@ -17940,7 +17968,7 @@
         <v>3024</v>
       </c>
     </row>
-    <row r="756" spans="1:4">
+    <row r="756" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A756" t="s">
         <v>758</v>
       </c>
@@ -17954,7 +17982,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="757" spans="1:4">
+    <row r="757" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A757" t="s">
         <v>759</v>
       </c>
@@ -17968,7 +17996,7 @@
         <v>3448</v>
       </c>
     </row>
-    <row r="758" spans="1:4">
+    <row r="758" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A758" t="s">
         <v>760</v>
       </c>
@@ -17982,7 +18010,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="759" spans="1:4">
+    <row r="759" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A759" t="s">
         <v>761</v>
       </c>
@@ -17996,7 +18024,7 @@
         <v>10710</v>
       </c>
     </row>
-    <row r="760" spans="1:4">
+    <row r="760" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A760" t="s">
         <v>762</v>
       </c>
@@ -18010,7 +18038,7 @@
         <v>10145</v>
       </c>
     </row>
-    <row r="761" spans="1:4">
+    <row r="761" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A761" t="s">
         <v>763</v>
       </c>
@@ -18024,7 +18052,7 @@
         <v>7780</v>
       </c>
     </row>
-    <row r="762" spans="1:4">
+    <row r="762" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A762" t="s">
         <v>764</v>
       </c>
@@ -18038,7 +18066,7 @@
         <v>3321</v>
       </c>
     </row>
-    <row r="763" spans="1:4">
+    <row r="763" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A763" t="s">
         <v>765</v>
       </c>
@@ -18052,7 +18080,7 @@
         <v>9300</v>
       </c>
     </row>
-    <row r="764" spans="1:4">
+    <row r="764" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A764" t="s">
         <v>766</v>
       </c>
@@ -18066,7 +18094,7 @@
         <v>3520</v>
       </c>
     </row>
-    <row r="765" spans="1:4">
+    <row r="765" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A765" t="s">
         <v>767</v>
       </c>
@@ -18080,7 +18108,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="766" spans="1:4">
+    <row r="766" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A766" t="s">
         <v>768</v>
       </c>
@@ -18094,7 +18122,7 @@
         <v>3520</v>
       </c>
     </row>
-    <row r="767" spans="1:4">
+    <row r="767" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A767" t="s">
         <v>769</v>
       </c>
@@ -18108,7 +18136,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="768" spans="1:4">
+    <row r="768" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A768" t="s">
         <v>770</v>
       </c>
@@ -18122,7 +18150,7 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="769" spans="1:4">
+    <row r="769" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A769" t="s">
         <v>771</v>
       </c>
@@ -18136,7 +18164,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="770" spans="1:4">
+    <row r="770" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A770" t="s">
         <v>772</v>
       </c>
@@ -18150,7 +18178,7 @@
         <v>5470</v>
       </c>
     </row>
-    <row r="771" spans="1:4">
+    <row r="771" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A771" t="s">
         <v>773</v>
       </c>
@@ -18164,7 +18192,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="772" spans="1:4">
+    <row r="772" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A772" t="s">
         <v>774</v>
       </c>
@@ -18178,7 +18206,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="773" spans="1:4">
+    <row r="773" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A773" t="s">
         <v>775</v>
       </c>
@@ -18192,7 +18220,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="774" spans="1:4">
+    <row r="774" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A774" t="s">
         <v>776</v>
       </c>
@@ -18206,7 +18234,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="775" spans="1:4">
+    <row r="775" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A775" t="s">
         <v>777</v>
       </c>
@@ -18220,7 +18248,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="776" spans="1:4">
+    <row r="776" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A776" t="s">
         <v>778</v>
       </c>
@@ -18234,7 +18262,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="777" spans="1:4">
+    <row r="777" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A777" t="s">
         <v>779</v>
       </c>
@@ -18249,6 +18277,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>